--- a/output/pdf_financials_xlsx/BOL.xlsx
+++ b/output/pdf_financials_xlsx/BOL.xlsx
@@ -6628,28 +6628,28 @@
         <v>0.41613</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>0</v>
+        <v>0.010242</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>0</v>
+        <v>-0.03343</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>0</v>
+        <v>0.033705</v>
       </c>
       <c r="I103" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J103" s="3" t="n">
-        <v>0</v>
+        <v>0.001371</v>
       </c>
       <c r="K103" s="3" t="n">
-        <v>0</v>
+        <v>-0.000165</v>
       </c>
       <c r="L103" s="3" t="n">
-        <v>0</v>
+        <v>7.6e-05</v>
       </c>
       <c r="M103" s="3" t="n">
-        <v>0</v>
+        <v>0.001277</v>
       </c>
       <c r="N103" s="1" t="inlineStr">
         <is>
@@ -6817,28 +6817,28 @@
         <v>0.424625</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>-0.140619</v>
+        <v>-0.130377</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>-0.086176</v>
+        <v>-0.119606</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0.101748</v>
+        <v>0.135453</v>
       </c>
       <c r="I106" s="3" t="n">
         <v>0.126323</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>0.013167</v>
+        <v>0.014538</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>0.052182</v>
+        <v>0.052017</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>0.040487</v>
+        <v>0.040563</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>0.082647</v>
+        <v>0.083924</v>
       </c>
       <c r="N106" s="1" t="inlineStr">
         <is>
@@ -9130,7 +9130,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>-</t>
@@ -14318,7 +14322,11 @@
           <t>Prepaid and deposits (Note 4)</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -23762,7 +23770,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr"/>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E161" t="inlineStr">
         <is>
           <t>-</t>
@@ -28664,7 +28676,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr"/>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E213" t="inlineStr">
         <is>
           <t>-</t>
@@ -33364,7 +33380,11 @@
           <t>Prepaid and deposits</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr"/>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E262" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/BOL.xlsx
+++ b/output/pdf_financials_xlsx/BOL.xlsx
@@ -1063,19 +1063,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.009852</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.00144</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>3.3e-05</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.00763</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.01173</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -2066,19 +2066,19 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.597672</v>
+        <v>-0.607524</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.337439</v>
+        <v>-0.338879</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.686063</v>
+        <v>-0.686096</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.287077</v>
+        <v>-1.294707</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.955528</v>
+        <v>-0.967258</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-0.540722</v>
@@ -2192,19 +2192,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.597672</v>
+        <v>-0.607524</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.337439</v>
+        <v>-0.338879</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.686063</v>
+        <v>-0.686096</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.287077</v>
+        <v>-1.294707</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.955528</v>
+        <v>-0.967258</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-0.540722</v>
@@ -2526,13 +2526,13 @@
         <v>0.116231</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.148922</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.043458</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.011649</v>
       </c>
       <c r="N34" s="1" t="inlineStr">
         <is>
@@ -2545,10 +2545,10 @@
         </is>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.021813</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.155012</v>
       </c>
     </row>
     <row r="35">
@@ -2644,13 +2644,13 @@
         <v>0.216231</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.010237</v>
+        <v>0.159159</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.002229</v>
+        <v>0.045687</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.011649</v>
       </c>
       <c r="N36" s="1" t="inlineStr">
         <is>
@@ -2663,10 +2663,10 @@
         </is>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.003979</v>
+        <v>0.025792</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0.00203</v>
+        <v>0.157042</v>
       </c>
     </row>
     <row r="37">
@@ -3352,13 +3352,13 @@
         <v>0.053192</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.1523</v>
+        <v>0.003378</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.04676</v>
+        <v>0.003302</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.013675</v>
+        <v>0.002026</v>
       </c>
       <c r="N48" s="1" t="inlineStr">
         <is>
@@ -3371,10 +3371,10 @@
         </is>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.025446</v>
+        <v>0.003633</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.168218</v>
+        <v>0.013206</v>
       </c>
     </row>
     <row r="49">
@@ -8852,7 +8852,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -42086,7 +42086,7 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
@@ -46776,7 +46776,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E403" s="5" t="n">

--- a/output/pdf_financials_xlsx/BOL.xlsx
+++ b/output/pdf_financials_xlsx/BOL.xlsx
@@ -748,10 +748,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.053877</v>
+        <v>0.062429</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.017009</v>
+        <v>0.038253</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0.16032</v>
@@ -1327,10 +1327,10 @@
         <v>-1.287077</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>-0.955528</v>
+        <v>-0.236123</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-0.540722</v>
+        <v>-0.415722</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>-5.767496</v>
@@ -1381,19 +1381,19 @@
         <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.126</v>
+        <v>-0.126</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>-0</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0.070051</v>
+        <v>-0.196</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.719405</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.125</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>-0</v>
@@ -2078,10 +2078,10 @@
         <v>-1.294707</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.967258</v>
+        <v>-0.247853</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.540722</v>
+        <v>-0.415722</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-5.767496</v>
@@ -2204,10 +2204,10 @@
         <v>-1.294707</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.967258</v>
+        <v>-0.247853</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.540722</v>
+        <v>-0.415722</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-5.767496</v>
@@ -2351,13 +2351,13 @@
         <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-5.442642514783498</v>
+        <v>-15.2283041340961</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>-0</v>
+        <v>-304.673835246884</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>-0</v>
+        <v>-30.06817055628521</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>-0</v>
@@ -2865,13 +2865,13 @@
         <v>0.019789</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>0.122072</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>0.209281</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>0.079626</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>0</v>
@@ -2924,13 +2924,13 @@
         <v>0.039578</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.166993</v>
+        <v>0.289065</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.277837</v>
+        <v>0.487118</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0.148997</v>
+        <v>0.228623</v>
       </c>
       <c r="I41" s="3" t="n">
         <v>0.024658</v>
@@ -3337,13 +3337,13 @@
         <v>0.098758</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.00486</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.03829</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.004585</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>0.004585</v>
@@ -7399,13 +7399,13 @@
         <v>0</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>0.210493</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>0.008007999999999999</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>0.00206</v>
       </c>
       <c r="N115" s="1" t="inlineStr">
         <is>
@@ -24036,7 +24036,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr"/>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E164" t="inlineStr">
         <is>
           <t>-</t>
@@ -27518,7 +27522,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr"/>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E201" t="inlineStr">
         <is>
           <t>-</t>
@@ -30888,7 +30896,11 @@
           <t>Future income recovery</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr"/>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E236" t="inlineStr">
         <is>
           <t>-</t>
@@ -33190,7 +33202,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr"/>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E260" t="inlineStr">
         <is>
           <t>-</t>
@@ -34934,7 +34950,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D278" t="inlineStr"/>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E278" t="inlineStr">
         <is>
           <t>-</t>
@@ -41216,7 +41236,11 @@
           <t>Deferred income tax recovery 10</t>
         </is>
       </c>
-      <c r="D345" t="inlineStr"/>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E345" t="inlineStr">
         <is>
           <t>-</t>
@@ -42556,7 +42580,11 @@
           <t>Deferred income tax recovery 13</t>
         </is>
       </c>
-      <c r="D359" t="inlineStr"/>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E359" t="inlineStr">
         <is>
           <t>-</t>
@@ -43708,7 +43736,11 @@
           <t>Future income tax recovery (Note 6(c))</t>
         </is>
       </c>
-      <c r="D371" t="inlineStr"/>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E371" t="inlineStr">
         <is>
           <t>-</t>
@@ -44566,7 +44598,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D380" t="inlineStr"/>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E380" t="inlineStr">
         <is>
           <t>-</t>
@@ -45134,7 +45170,11 @@
           <t>Future income tax recovery (Note 9)</t>
         </is>
       </c>
-      <c r="D386" t="inlineStr"/>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E386" t="inlineStr">
         <is>
           <t>-</t>
@@ -46100,7 +46140,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D396" t="inlineStr"/>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E396" s="5" t="n">
         <v>0.008552000000000001</v>
       </c>
@@ -47254,7 +47298,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D408" t="inlineStr"/>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E408" t="inlineStr">
         <is>
           <t>-</t>
